--- a/Excel/const@全局常量.xlsx
+++ b/Excel/const@全局常量.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\work\github\xls2cfg\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="13575"/>
+    <workbookView windowWidth="28800" windowHeight="14175"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -62,16 +67,16 @@
     <t>value</t>
   </si>
   <si>
+    <t>desc</t>
+  </si>
+  <si>
     <t>tags</t>
   </si>
   <si>
-    <t>desc</t>
-  </si>
-  <si>
     <t>##end</t>
   </si>
   <si>
-    <t>createRoleResurces</t>
+    <t>createRoleResources</t>
   </si>
   <si>
     <t>list&lt;list&lt;int32&gt;&gt;</t>
@@ -89,10 +94,10 @@
     <t>int32</t>
   </si>
   <si>
+    <t>跳过战斗需要的回合数</t>
+  </si>
+  <si>
     <t>s</t>
-  </si>
-  <si>
-    <t>跳过战斗需要的回合数</t>
   </si>
 </sst>
 </file>
@@ -1111,8 +1116,8 @@
   <cols>
     <col min="1" max="1" width="22.5416666666667" style="1" customWidth="1"/>
     <col min="2" max="3" width="17.875" customWidth="1"/>
-    <col min="4" max="4" width="28.3666666666667" style="1" customWidth="1"/>
-    <col min="5" max="5" width="24.1833333333333" style="1" customWidth="1"/>
+    <col min="4" max="4" width="24.1833333333333" style="1" customWidth="1"/>
+    <col min="5" max="5" width="28.3666666666667" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.75" customHeight="1" spans="1:6">
@@ -1145,7 +1150,7 @@
       <c r="C2" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>9</v>
       </c>
     </row>
